--- a/xls/square_16_tri3_18.xlsx
+++ b/xls/square_16_tri3_18.xlsx
@@ -482,13 +482,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.7567428540168508</v>
+        <v>-0.7567467064473754</v>
       </c>
       <c r="J18">
-        <v>-2.102809329356524</v>
+        <v>-2.1028089922423323</v>
       </c>
       <c r="K18">
-        <v>0.7596260636705868</v>
+        <v>0.7596265911748541</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-2.531725288248809</v>
+        <v>-2.5317258596497307</v>
       </c>
       <c r="J19">
-        <v>-2.0901329580990695</v>
+        <v>-2.0901325514420526</v>
       </c>
       <c r="K19">
-        <v>0.6562992956757366</v>
+        <v>0.6563066707249944</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-2.4750419235175354</v>
+        <v>-2.4750431903282526</v>
       </c>
       <c r="J20">
-        <v>-2.040770450785541</v>
+        <v>-2.040770340704422</v>
       </c>
       <c r="K20">
-        <v>1.4701262140185223</v>
+        <v>1.470126653449135</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-2.2505508951435065</v>
+        <v>-2.2505506522434353</v>
       </c>
       <c r="J21">
-        <v>-1.812416465020576</v>
+        <v>-1.8124164525261837</v>
       </c>
       <c r="K21">
-        <v>2.4244448293662444</v>
+        <v>2.4244448185533933</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-1.5459178249567367</v>
+        <v>-1.5459177445107863</v>
       </c>
       <c r="J22">
-        <v>-1.335297132833318</v>
+        <v>-1.3352971046354947</v>
       </c>
       <c r="K22">
-        <v>3.139368135772295</v>
+        <v>3.139368153750308</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -657,13 +657,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.8987209800159801</v>
+        <v>-0.8987211419617408</v>
       </c>
       <c r="J23">
-        <v>-0.7962716987434272</v>
+        <v>-0.7962717941690111</v>
       </c>
       <c r="K23">
-        <v>3.6495696284718764</v>
+        <v>3.6495696530580477</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -692,13 +692,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.39436964085302423</v>
+        <v>-0.3943696321364682</v>
       </c>
       <c r="J24">
-        <v>-0.330384747240621</v>
+        <v>-0.33038474077142616</v>
       </c>
       <c r="K24">
-        <v>3.9108473643247854</v>
+        <v>3.9108473579600047</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -727,13 +727,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.01337110850627544</v>
+        <v>-0.01337110852223832</v>
       </c>
       <c r="J25">
-        <v>-0.013106302235895779</v>
+        <v>-0.013106302231664714</v>
       </c>
       <c r="K25">
-        <v>3.4921567831626885</v>
+        <v>3.4921567824625255</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -762,13 +762,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.017132335875620006</v>
+        <v>-0.017132335849213382</v>
       </c>
       <c r="J26">
-        <v>-0.015488226796685805</v>
+        <v>-0.015488226779978109</v>
       </c>
       <c r="K26">
-        <v>3.508600222056128</v>
+        <v>3.5086002219549974</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -797,13 +797,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.004086380490501864</v>
+        <v>-0.004086380519558287</v>
       </c>
       <c r="J27">
-        <v>-0.0030938615826857554</v>
+        <v>-0.003093861602971227</v>
       </c>
       <c r="K27">
-        <v>3.0652759915468684</v>
+        <v>3.065275993996288</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -832,13 +832,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.0009708763565052989</v>
+        <v>-0.000970876355924006</v>
       </c>
       <c r="J28">
-        <v>-0.0007699299507172359</v>
+        <v>-0.0007699299503385488</v>
       </c>
       <c r="K28">
-        <v>2.804810335912521</v>
+        <v>2.8048103358581233</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -867,13 +867,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-0.0012011260456423764</v>
+        <v>-0.0012011260438325908</v>
       </c>
       <c r="J29">
-        <v>-0.0008708799388822973</v>
+        <v>-0.000870879937671473</v>
       </c>
       <c r="K29">
-        <v>2.780960679234314</v>
+        <v>2.780960678870546</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -902,13 +902,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.00098279896185752</v>
+        <v>-0.0009827989618973888</v>
       </c>
       <c r="J30">
-        <v>-0.000779365520069045</v>
+        <v>-0.0007793655201013114</v>
       </c>
       <c r="K30">
-        <v>2.806665237197515</v>
+        <v>2.8066652372889798</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -937,13 +937,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-0.0003041891085806489</v>
+        <v>-0.00030418910857997337</v>
       </c>
       <c r="J31">
-        <v>-0.00024690476526295434</v>
+        <v>-0.000246904765263292</v>
       </c>
       <c r="K31">
-        <v>2.587717670771093</v>
+        <v>2.587717670927619</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -972,13 +972,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.0011696652179153904</v>
+        <v>-0.0011696652171049597</v>
       </c>
       <c r="J32">
-        <v>-0.0009307790408485049</v>
+        <v>-0.0009307790403455922</v>
       </c>
       <c r="K32">
-        <v>2.8480867522397566</v>
+        <v>2.8480867519458326</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_18.xlsx
+++ b/xls/square_16_tri3_18.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>361</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>289</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>289</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>1536</v>
+      </c>
+      <c r="I16">
+        <v>2.8282690521353353</v>
+      </c>
+      <c r="J16">
+        <v>-0.5100368051720802</v>
+      </c>
+      <c r="K16">
+        <v>0.775061914423921</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>361</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>289</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>1734</v>
+      </c>
+      <c r="I17">
+        <v>1.1686748345492612</v>
+      </c>
+      <c r="J17">
+        <v>-1.5509373538148268</v>
+      </c>
+      <c r="K17">
+        <v>1.406954244681986</v>
+      </c>
+    </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>11</v>
